--- a/important_mails_2026-08-05.xlsx
+++ b/important_mails_2026-08-05.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H305"/>
+  <dimension ref="A1:H307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -500,21 +500,122 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Wed, 5 Aug 2026 05:00:39 +0000</t>
+          <t>Wed, 5 Aug 2026 12:58:13 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>"Amazon Seller Central Notifications(Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Dangerous goods (hazmat) status update</t>
+          <t>EPR Pay on Behalf charges for 2025 Amazon.fr sales</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe
+ 96
+ You’ll be charged for EPR eco-contribution fees paid on your behalf for sales on Amazon.fr in 2025 and EPR Pay on Behalf service fees
+ You’ll be charged for EPR eco-contribution fees paid on your behalf for sales on Amazon.fr in 2025 and EPR Pay on Behalf service fees
+ Reading Time: 1 minute 30 seconds
+ Hello,
+Between August and September 2026, you’ll be charged eco-contribution fees for your sales of products subject to Extended Producer Responsibility (EPR) obligations on Amazon.fr in 2025, along with EPR Pay on Behalf service fees, for the following categories:
+ - Sports
+ - Do-it-yourself (DIY)
+ Why will I be charged?
+ In line with EPR regulation, producers must pay eco-contribution fees to Producer Responsibility Organizations (PROs) for sales of affected products on Amazon.fr. As previously communicated, you were automatically enrolled in Amazon’s EPR Pay on Behalf service, and Amazon paid eco-contribution fees for your sales, because you met all of the following criteria:
+ You were considered a producer under Environmental Code.
+ You sold products subject to EPR obligations on Amazon.fr in the above categories.
+ You didn’t submit a valid EPR Registration Nu</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 5 Aug 2026 12:33:41 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów
+ Dzień dobry Weihai EU,
+ Niektóre z Twoich ofert zostały zdezaktywowane w naszych sklepach w Unii Europejskiej (UE) z powodu braku informacji o zgodności z wymogami. Działania te nie mają wpływu na kondycję Twojego konta.
+ Przykłady zdezaktywowanych ofert znajdziesz na dole tej wiadomości e-mail. Aby wyświetlić ich pełną listę, przejdź na stronę „Kondycja konta”. Aby spełnić wymogi rozporządzenia w sprawie ogólnego bezpieczeństwa produktów, zapoznaj się z poniższymi ofertami i dalszymi działaniami do wykonania.
+ Prześlij informacje dotyczące zgodności z wymogami
+ Prześlij informacje dotyczące zgodności z wymogami
+ Jak mogę ponownie aktywować oferty produktów?
+ Aby ponownie aktywować oferty, dostarcz obowiązkowe informacje dotyczące zgodności z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów, postępując zgodnie z poniższymi instrukcjami:
+-
+ Przejdź na stronę Kondycja konta .
+- Wybierz „Dodaj filtry” i w kolumnie „Filtruj według podjętego działania” zaznacz pole „Usunięto ofertę”.
+- Obok zdezaktywowanej oferty produktu kliknij „Prześlij” i postępuj zg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 5 Aug 2026 05:00:39 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon Seller Central Notifications(Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Dangerous goods (hazmat) status update</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -539,39 +640,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Wed, 5 Aug 2026 01:53:21 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Actualización de estado de mercancías peligrosas</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>96
  Actualización de estado de mercancías peligrosas
@@ -595,39 +696,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Wed, 5 Aug 2026 01:47:30 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Statusuppdatering för farligt gods</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
  Statusuppdatering för farligt gods
@@ -652,39 +753,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Wed, 5 Aug 2026 01:43:13 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>亚马逊卖家平台通知（请勿回复） &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>危险物品（危险品）状态更新</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
  危险物品（危险品）状态更新
@@ -739,39 +840,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Wed, 5 Aug 2026 01:20:28 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Status materiałów niebezpiecznych (hazmat)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
  Status materiałów niebezpiecznych (hazmat)
@@ -795,39 +896,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Wed, 5 Aug 2026 01:19:40 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -852,39 +953,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Wed, 5 Aug 2026 01:19:38 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -909,39 +1010,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Wed, 5 Aug 2026 01:19:35 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>亚马逊卖家平台通知（请勿回复） &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>危险品状态更新</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  危险品状态更新
@@ -985,39 +1086,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Wed, 5 Aug 2026 01:04:56 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications(Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dangerous goods (hazmat) status update
@@ -1042,39 +1143,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Wed, 5 Aug 2026 01:04:53 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications(Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dangerous goods (hazmat) status update
@@ -1099,39 +1200,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Wed, 5 Aug 2026 01:02:01 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Aggiornamento dello stato delle merci pericolose</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
  Aggiornamento dello stato delle merci pericolose
@@ -1155,39 +1256,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Wed, 5 Aug 2026 01:01:52 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Update van status gevaarlijke goederen</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
  Update van status gevaarlijke goederen
@@ -1212,39 +1313,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Wed, 5 Aug 2026 01:46:30 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Mise à jour du statut de matières dangereuses</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
  Mise à jour du statut de matières dangereuses
@@ -1270,39 +1371,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Tue, 4 Aug 2026 04:57:39 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1318,39 +1419,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 16:27:49 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (3rwPw0NlBZ)</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1370,39 +1471,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 04:52:33 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1418,39 +1519,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 04:46:25 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1466,39 +1567,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 04:49:15 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1514,39 +1615,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Fri, 31 Jul 2026 09:23:20 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1562,39 +1663,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 19:42:31 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (YsvR7aqoWy)</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1619,39 +1720,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 07:19:03 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (8AOhKJjKS4)</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1671,39 +1772,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 05:45:50 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1719,39 +1820,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:56:25 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>"Amazon.sa" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Your Amazon bank account information has been successfully updated</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  Your Amazon bank account information has been successfully updated
@@ -1767,39 +1868,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:49:41 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>"Amazon.fr" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Account Protection</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon Seller Account Protection
@@ -1816,39 +1917,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:48:37 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>"Amazon.ae" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Your Amazon bank account information has been successfully updated</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  Your Amazon bank account information has been successfully updated
@@ -1864,39 +1965,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:43:00 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Your Amazon bank account information has been updated successfully</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  Your Amazon bank account information has been updated successfully
@@ -1912,39 +2013,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:38:29 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Your Amazon bank account information has been updated successfully</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
  Your Amazon bank account information has been updated successfully
@@ -1960,92 +2061,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 29 Jul 2026 14:56:26 +0000</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Automated unfulfillable FBA inventory removal notification</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai US,
-The following automated unfulfillable FBA removal orders have been created based on your automated settings.
- Removal order ID YsvR7aqoWy
- You can view the removals on Removal Order Details in your seller account by using the Search tool.
-The next removal order will be created as scheduled on July 30, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
-To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
- Thank you.
-The Fulfillment by Amazon team
-Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
- SPC-USAmazon-123147537484532</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Tue, 4 Aug 2026 12:59:47 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2062,39 +2110,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 12:39:35 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Final week of early-bird pricing for Amazon Accelerate 2026—ends August 8</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-29/7z4ytv7/6806510535/h/ebUC-rn_gdmnOZgc0Tgqz8DiEn0AwvkMsQeazFirtjo)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4ytvb/6806510535/h/ebUC-rn_gdmnOZgc0Tgqz8DiEn0AwvkMsQeazFirtjo)
@@ -2113,39 +2161,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 12:14:10 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2165,39 +2213,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 12:13:54 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2214,39 +2262,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 09:02:05 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Managing compliance across Europe? There's a simpler way.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Managing compliance across Europe? There's a simpler way.
  96
@@ -2256,39 +2304,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Fri, 31 Jul 2026 12:51:30 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Early-bird pricing ends August 8. Save $100 before the price goes up</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-29/7z4ytt4/6801785250/h/cuj5ZID4pxnaoQxnGKVediz6maB8MtzjCTkMytKZvg4)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4ytt7/6801785250/h/cuj5ZID4pxnaoQxnGKVediz6maB8MtzjCTkMytKZvg4)
@@ -2305,39 +2353,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 14:27:09 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2357,39 +2405,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 12:05:29 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Get 1:1 guidance from Amazon experts. Book your Seller Café appointment now</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-27/7z4wb13/6798182481/h/05AL5iRkNxOUgud3Z_einTRfylmI-j5cIlGQkJP8RGs)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4wb16/6798182481/h/05AL5iRkNxOUgud3Z_einTRfylmI-j5cIlGQkJP8RGs)
@@ -2405,39 +2453,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 06:58:29 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your information is verified – Start selling on Amazon now</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Seller,
@@ -2459,39 +2507,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Tue, 4 Aug 2026 18:16:42 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2510,39 +2558,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Tue, 4 Aug 2026 17:58:25 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2561,39 +2609,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 17:55:58 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2612,39 +2660,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 17:41:59 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2663,39 +2711,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 15:45:25 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -2722,39 +2770,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 09:15:08 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2772,39 +2820,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 03:48:43 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -2832,39 +2880,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 00:32:40 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2882,39 +2930,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 00:25:49 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2932,39 +2980,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 16:15:51 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -2982,39 +3030,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 15:08:44 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
  Hello xiao jianming,
@@ -3033,39 +3081,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 15:08:23 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Action required: Notification of ASIN removal</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello xiao jianming,
@@ -3081,39 +3129,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:23:21 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3131,39 +3179,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:17:26 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3181,39 +3229,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:16:37 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Action required: Notification of ASIN removal</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3229,39 +3277,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:10:39 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Action required: Notification of ASIN removal</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3274,64 +3322,6 @@
  To see the list of impacted ASINs in each store and reactivate your products, submit the required compliance documents by clicking ‘Add or appeal compliance’ next to the impacted ASIN on your ‘Manage your Compliance’ dashboard .
  We can only reinstate products that fulfil all relevant legal requirements for sale. Close, delete, or archive any non-compliant listings that you do not intend to sell or appeal in the future.
  What happens if I</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 29 Jul 2026 09:26:45 +0000</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>"toys-safety-mv@amazon.de" &lt;toys-safety-mv@amazon.de&gt;</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>RE:[CASE 13104358872] SELLER: A1UYGOR4ZW45MU, ASIN: B0F13M1H6F,
- MARKETPLACE: 4 - PS - APPEAL</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>96
-RE:[CASE 13104358872] SELLER: A1UYGOR4ZW45MU, ASIN: B0F13M1H6F, MARKETPLACE: 4 - PS - APPEAL
-Dear Selling Partner,
-Thank you for your interest in selling on Amazon.
-Based on currently available information, the product you want to sell does not raise concerns for the applied product category.
-Therefore, your ASIN has been approved for this product category. However, your product may fall under other Product Category Policies which require compliance documentation. You will be notified of any further compliance requirements.
-Please allow up to 48 hours for the ASIN to appear on the website.
-We appreciate your cooperation on this important matter.
-To help us continually improve, we ask that you take a moment to complete our survey below. This would help us understand your overall compliance experience.
-Were you satisfied with the support provided?
-If yes, please click here:
- http://www.amazon.de/gp/help/survey?p=A2V21SVDLWRRYT&amp;k=hy
-If no, please click here:
- http://www.amazon.de/gp/help/survey?p=A2V21SVDLWRRYT&amp;k=hn
-Freundliche Grüße
-Narcis T.
-Amazon Verkäuferservice
-=======================================
-BENÖTIGEN SIE WEITERE HILFE?
-In den Verkäuferforen erhalten Sie Tipps und Hi</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5364,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5389,63 +5379,21 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 11:26:20 +0000</t>
+          <t>Sat, 1 Aug 2026 04:26:40 +0000</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Ukończ rejestrację opakowań UE według kraju</t>
+          <t>Create FBA removal order by 2026-08-13</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>Ukończ rejestrację opakowań UE według kraju
- 96
- Kroki dla poszczególnych krajów, aby uzyskać numer rejestracyjny EPR do 12 sierpnia 2026 r.
-                                                     ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­
- Kroki dla poszczeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 1 Aug 2026 04:26:40 +0000</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-08-13</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -5469,39 +5417,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 03:08:11 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -5525,39 +5473,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:17:46 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>View your US Q3-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q3-2026
@@ -5584,6 +5532,59 @@
 - Reduce contact and return rates
  Follow these practices to prevent customer confusion and minimize your workload:
 - Monitor the Response Needed inbox within the Buyer-Seller Messaging Service . In the rare case that we need your he</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 29 Jul 2026 14:56:26 +0000</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Automated unfulfillable FBA inventory removal notification</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+The following automated unfulfillable FBA removal orders have been created based on your automated settings.
+ Removal order ID YsvR7aqoWy
+ You can view the removals on Removal Order Details in your seller account by using the Search tool.
+The next removal order will be created as scheduled on July 30, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
+To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
+ Thank you.
+The Fulfillment by Amazon team
+Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
+ SPC-USAmazon-123147537484532</t>
         </is>
       </c>
     </row>
@@ -10597,21 +10598,79 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Fri, 24 Jul 2026 14:11:48 +0000</t>
+          <t>Wed, 29 Jul 2026 09:26:45 +0000</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
+          <t>"toys-safety-mv@amazon.de" &lt;toys-safety-mv@amazon.de&gt;</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>You asked for smarter AI tools. We're delivering at Accelerate 2026</t>
+          <t>RE:[CASE 13104358872] SELLER: A1UYGOR4ZW45MU, ASIN: B0F13M1H6F,
+ MARKETPLACE: 4 - PS - APPEAL</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr"/>
       <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>96
+RE:[CASE 13104358872] SELLER: A1UYGOR4ZW45MU, ASIN: B0F13M1H6F, MARKETPLACE: 4 - PS - APPEAL
+Dear Selling Partner,
+Thank you for your interest in selling on Amazon.
+Based on currently available information, the product you want to sell does not raise concerns for the applied product category.
+Therefore, your ASIN has been approved for this product category. However, your product may fall under other Product Category Policies which require compliance documentation. You will be notified of any further compliance requirements.
+Please allow up to 48 hours for the ASIN to appear on the website.
+We appreciate your cooperation on this important matter.
+To help us continually improve, we ask that you take a moment to complete our survey below. This would help us understand your overall compliance experience.
+Were you satisfied with the support provided?
+If yes, please click here:
+ http://www.amazon.de/gp/help/survey?p=A2V21SVDLWRRYT&amp;k=hy
+If no, please click here:
+ http://www.amazon.de/gp/help/survey?p=A2V21SVDLWRRYT&amp;k=hn
+Freundliche Grüße
+Narcis T.
+Amazon Verkäuferservice
+=======================================
+BENÖTIGEN SIE WEITERE HILFE?
+In den Verkäuferforen erhalten Sie Tipps und Hi</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 24 Jul 2026 14:11:48 +0000</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>You asked for smarter AI tools. We're delivering at Accelerate 2026</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-22/7z4t8v9/6787753082/h/IGusOwCMHYF897jTLiEldN8I_908U5ToWDqeOf0umps)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4t8vd/6787753082/h/IGusOwCMHYF897jTLiEldN8I_908U5ToWDqeOf0umps)
@@ -10627,39 +10686,39 @@
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 23:12:37 +0000</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr"/>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -10678,39 +10737,39 @@
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 12:38:11 +0000</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr"/>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -10726,39 +10785,39 @@
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 09:21:24 +0000</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13075958512] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr"/>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 13075958512] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规
@@ -10793,39 +10852,39 @@
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Jul 2026 23:10:13 +0000</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr"/>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -10844,39 +10903,39 @@
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Jul 2026 19:11:54 +0000</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr"/>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -10894,39 +10953,39 @@
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Jul 2026 19:09:21 +0000</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr"/>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -10944,39 +11003,39 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 12:36:12 +0000</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr"/>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -10992,39 +11051,39 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>Wed, 15 Jul 2026 06:06:37 +0000</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr"/>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -11043,40 +11102,40 @@
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 15:01:39 +0000</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>Manage VAT &amp; EPR Requirements Directly Within Your Pan-European FBA
  Inventory Portal</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr"/>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>Visit the Pan-EU Portal to Manage Listings,﻿ Compliance &amp;amp; Expansion in EU
                                                     ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­
@@ -11084,39 +11143,39 @@
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 17:38:33 +0000</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="F207" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr"/>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -11136,39 +11195,39 @@
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 16:17:59 +0000</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="F208" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr"/>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -11188,39 +11247,39 @@
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 05:08:36 +0000</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="F209" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr"/>
-      <c r="H208" s="2" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -11239,40 +11298,40 @@
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 13:22:39 +0000</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>Get answers from the people who build the tools you use every day.
  Save $100</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr"/>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="G210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EM/7z49s9x/6752554013/h/2aeQsjjzcdEfNdbvcpArxhFF9Du4sBW3WI4zsTSQPBE)
 [Speakers at Accelerate](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4bmtj/6752554013/h/2aeQsjjzcdEfNdbvcpArxhFF9Du4sBW3WI4zsTSQPBE)
@@ -11289,39 +11348,39 @@
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 13:08:44 +0000</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr"/>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -11340,40 +11399,40 @@
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 08:00:54 +0000</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F211" s="2" t="inlineStr">
+      <c r="F212" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr"/>
-      <c r="H211" s="2" t="inlineStr">
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -11388,40 +11447,40 @@
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 05:35:29 +0000</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F212" s="2" t="inlineStr">
+      <c r="F213" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr"/>
-      <c r="H212" s="2" t="inlineStr">
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -11446,39 +11505,81 @@
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 29 Jul 2026 11:26:20 +0000</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>Ukończ rejestrację opakowań UE według kraju</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>Ukończ rejestrację opakowań UE według kraju
+ 96
+ Kroki dla poszczególnych krajów, aby uzyskać numer rejestracyjny EPR do 12 sierpnia 2026 r.
+                                                     ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­
+ Kroki dla poszczeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Jul 2026 17:52:28 +0000</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="E215" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F213" s="2" t="inlineStr">
+      <c r="F215" s="2" t="inlineStr">
         <is>
           <t>Presentar información de cumplimiento normativo de la RAP en Portugal</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr"/>
-      <c r="H213" s="2" t="inlineStr">
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr">
         <is>
           <t>96
  La normativa portuguesa sobre la RAP se aplica a los productos vendidos a clientes de Portugal.
@@ -11495,39 +11596,39 @@
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 14:31:45 +0000</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F214" s="2" t="inlineStr">
+      <c r="F216" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr"/>
-      <c r="H214" s="2" t="inlineStr">
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -11542,39 +11643,39 @@
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D215" s="2" t="inlineStr">
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 14:28:11 +0000</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F215" s="2" t="inlineStr">
+      <c r="F217" s="2" t="inlineStr">
         <is>
           <t>Seller News: July 2026</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr"/>
-      <c r="H215" s="2" t="inlineStr">
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr">
         <is>
           <t>Seller News: July 2026
  96
@@ -11584,39 +11685,39 @@
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 08:09:30 +0000</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F216" s="2" t="inlineStr">
+      <c r="F218" s="2" t="inlineStr">
         <is>
           <t>Seller News: July 2026</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr"/>
-      <c r="H216" s="2" t="inlineStr">
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Seller News: July 2026
  96
@@ -11625,39 +11726,39 @@
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D217" s="2" t="inlineStr">
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Jul 2026 19:14:46 +0000</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F217" s="2" t="inlineStr">
+      <c r="F219" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr"/>
-      <c r="H217" s="2" t="inlineStr">
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -11673,40 +11774,40 @@
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Jul 2026 19:13:33 +0000</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr">
+      <c r="F220" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr"/>
-      <c r="H218" s="2" t="inlineStr">
+      <c r="G220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -11722,39 +11823,39 @@
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Jul 2026 19:11:38 +0000</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F219" s="2" t="inlineStr">
+      <c r="F221" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G219" s="2" t="inlineStr"/>
-      <c r="H219" s="2" t="inlineStr">
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -11768,39 +11869,39 @@
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Jul 2026 19:11:18 +0000</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F220" s="2" t="inlineStr">
+      <c r="F222" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr"/>
-      <c r="H220" s="2" t="inlineStr">
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -11816,40 +11917,40 @@
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D221" s="2" t="inlineStr">
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Jul 2026 19:09:21 +0000</t>
         </is>
       </c>
-      <c r="E221" s="2" t="inlineStr">
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F221" s="2" t="inlineStr">
+      <c r="F223" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G221" s="2" t="inlineStr"/>
-      <c r="H221" s="2" t="inlineStr">
+      <c r="G223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -11865,39 +11966,39 @@
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D222" s="2" t="inlineStr">
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Jul 2026 19:08:32 +0000</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F222" s="2" t="inlineStr">
+      <c r="F224" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G222" s="2" t="inlineStr"/>
-      <c r="H222" s="2" t="inlineStr">
+      <c r="G224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -11913,39 +12014,39 @@
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Jul 2026 13:53:00 +0000</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F223" s="2" t="inlineStr">
+      <c r="F225" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G223" s="2" t="inlineStr"/>
-      <c r="H223" s="2" t="inlineStr">
+      <c r="G225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -11960,39 +12061,39 @@
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Jul 2026 11:19:50 +0000</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>Global Warehousing and Distribution &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F224" s="2" t="inlineStr">
+      <c r="F226" s="2" t="inlineStr">
         <is>
           <t>Global Warehousing and Distribution’s new China shipping options are live</t>
         </is>
       </c>
-      <c r="G224" s="2" t="inlineStr"/>
-      <c r="H224" s="2" t="inlineStr">
+      <c r="G226" s="2" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr">
         <is>
           <t>96
  Choose Shanghai or Shenzhen with Free on Board support
@@ -12007,39 +12108,39 @@
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D225" s="2" t="inlineStr">
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
         <is>
           <t>Wed, 15 Jul 2026 12:22:37 +0000</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F225" s="2" t="inlineStr">
+      <c r="F227" s="2" t="inlineStr">
         <is>
           <t>Introducing the Improved Similar Items Dashboard – Smarter Pricing Starts Now</t>
         </is>
       </c>
-      <c r="G225" s="2" t="inlineStr"/>
-      <c r="H225" s="2" t="inlineStr">
+      <c r="G227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo]
 We're excited to announce the launch of the improved Similar Items Dashboard. It helps you understand how comparable products are priced on Amazon. Instead of spending hours on manual research, it provides quick access to Amazon data – all in one place.
@@ -12057,40 +12158,40 @@
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D226" s="2" t="inlineStr">
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>Wed, 15 Jul 2026 10:17:38 +0000</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F226" s="2" t="inlineStr">
+      <c r="F228" s="2" t="inlineStr">
         <is>
           <t>Get increased New Selection Program (2026) benefits starting July
  30</t>
         </is>
       </c>
-      <c r="G226" s="2" t="inlineStr"/>
-      <c r="H226" s="2" t="inlineStr">
+      <c r="G228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr">
         <is>
           <t>96
  Effective July 30, 2026, the New Selection Program (2026) launches with increased benefits to help you launch new branded products with reduced costs and complexity while boosting early sales.
@@ -12104,39 +12205,39 @@
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D227" s="2" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Jul 2026 17:10:46 +0000</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F227" s="2" t="inlineStr">
+      <c r="F229" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr"/>
-      <c r="H227" s="2" t="inlineStr">
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -12152,40 +12253,40 @@
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D228" s="2" t="inlineStr">
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 22:17:55 +0000</t>
         </is>
       </c>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="E230" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F228" s="2" t="inlineStr">
+      <c r="F230" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Credit Note for
  6/2026</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr"/>
-      <c r="H228" s="2" t="inlineStr">
+      <c r="G230" s="2" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Credit Note for 6/2026
  96
@@ -12207,39 +12308,39 @@
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B229" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C229" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D229" s="2" t="inlineStr">
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 15:24:05 +0000</t>
         </is>
       </c>
-      <c r="E229" s="2" t="inlineStr">
+      <c r="E231" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F229" s="2" t="inlineStr">
+      <c r="F231" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr"/>
-      <c r="H229" s="2" t="inlineStr">
+      <c r="G231" s="2" t="inlineStr"/>
+      <c r="H231" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 6/2026
  96
@@ -12261,39 +12362,39 @@
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B230" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D230" s="2" t="inlineStr">
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 14:31:47 +0000</t>
         </is>
       </c>
-      <c r="E230" s="2" t="inlineStr">
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F230" s="2" t="inlineStr">
+      <c r="F232" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G230" s="2" t="inlineStr"/>
-      <c r="H230" s="2" t="inlineStr">
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -12308,40 +12409,40 @@
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B231" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D231" s="2" t="inlineStr">
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 23:30:27 +0000</t>
         </is>
       </c>
-      <c r="E231" s="2" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F231" s="2" t="inlineStr">
+      <c r="F233" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G231" s="2" t="inlineStr"/>
-      <c r="H231" s="2" t="inlineStr">
+      <c r="G233" s="2" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -12359,39 +12460,39 @@
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B232" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C232" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D232" s="2" t="inlineStr">
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 20:04:53 +0000</t>
         </is>
       </c>
-      <c r="E232" s="2" t="inlineStr">
+      <c r="E234" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F232" s="2" t="inlineStr">
+      <c r="F234" s="2" t="inlineStr">
         <is>
           <t>Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr"/>
-      <c r="H232" s="2" t="inlineStr">
+      <c r="G234" s="2" t="inlineStr"/>
+      <c r="H234" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist
@@ -12410,39 +12511,39 @@
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B233" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C233" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D233" s="2" t="inlineStr">
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 15:47:06 +0000</t>
         </is>
       </c>
-      <c r="E233" s="2" t="inlineStr">
+      <c r="E235" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F233" s="2" t="inlineStr">
+      <c r="F235" s="2" t="inlineStr">
         <is>
           <t>Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr"/>
-      <c r="H233" s="2" t="inlineStr">
+      <c r="G235" s="2" t="inlineStr"/>
+      <c r="H235" s="2" t="inlineStr">
         <is>
           <t>96
  Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów
@@ -12460,39 +12561,39 @@
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D234" s="2" t="inlineStr">
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 14:10:23 +0000</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F234" s="2" t="inlineStr">
+      <c r="F236" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr"/>
-      <c r="H234" s="2" t="inlineStr">
+      <c r="G236" s="2" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -12510,39 +12611,39 @@
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C235" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D235" s="2" t="inlineStr">
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 12:46:14 +0000</t>
         </is>
       </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F235" s="2" t="inlineStr">
+      <c r="F237" s="2" t="inlineStr">
         <is>
           <t>Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs</t>
         </is>
       </c>
-      <c r="G235" s="2" t="inlineStr"/>
-      <c r="H235" s="2" t="inlineStr">
+      <c r="G237" s="2" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr">
         <is>
           <t>96
  Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs
@@ -12561,39 +12662,39 @@
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B236" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D236" s="2" t="inlineStr">
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 10:28:11 +0000</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="E238" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F236" s="2" t="inlineStr">
+      <c r="F238" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G236" s="2" t="inlineStr"/>
-      <c r="H236" s="2" t="inlineStr">
+      <c r="G238" s="2" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -12612,39 +12713,39 @@
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D237" s="2" t="inlineStr">
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 09:08:55 +0000</t>
         </is>
       </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F237" s="2" t="inlineStr">
+      <c r="F239" s="2" t="inlineStr">
         <is>
           <t>Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise</t>
         </is>
       </c>
-      <c r="G237" s="2" t="inlineStr"/>
-      <c r="H237" s="2" t="inlineStr">
+      <c r="G239" s="2" t="inlineStr"/>
+      <c r="H239" s="2" t="inlineStr">
         <is>
           <t>96
  Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise
@@ -12663,39 +12764,39 @@
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D238" s="2" t="inlineStr">
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 08:53:55 +0000</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>亚马逊卖家平台通知 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F238" s="2" t="inlineStr">
+      <c r="F240" s="2" t="inlineStr">
         <is>
           <t>解决定价错误以重新启售停售商品</t>
         </is>
       </c>
-      <c r="G238" s="2" t="inlineStr"/>
-      <c r="H238" s="2" t="inlineStr">
+      <c r="G240" s="2" t="inlineStr"/>
+      <c r="H240" s="2" t="inlineStr">
         <is>
           <t>96
  因错价而被禁止显示
@@ -12733,40 +12834,40 @@
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D239" s="2" t="inlineStr">
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 20:45:55 +0000</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr">
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F239" s="2" t="inlineStr">
+      <c r="F241" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G239" s="2" t="inlineStr"/>
-      <c r="H239" s="2" t="inlineStr">
+      <c r="G241" s="2" t="inlineStr"/>
+      <c r="H241" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -12784,39 +12885,39 @@
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 18:16:40 +0000</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="E242" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F240" s="2" t="inlineStr">
+      <c r="F242" s="2" t="inlineStr">
         <is>
           <t>Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist</t>
         </is>
       </c>
-      <c r="G240" s="2" t="inlineStr"/>
-      <c r="H240" s="2" t="inlineStr">
+      <c r="G242" s="2" t="inlineStr"/>
+      <c r="H242" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist
@@ -12835,39 +12936,39 @@
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D241" s="2" t="inlineStr">
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 14:45:21 +0000</t>
         </is>
       </c>
-      <c r="E241" s="2" t="inlineStr">
+      <c r="E243" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F241" s="2" t="inlineStr">
+      <c r="F243" s="2" t="inlineStr">
         <is>
           <t>Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów</t>
         </is>
       </c>
-      <c r="G241" s="2" t="inlineStr"/>
-      <c r="H241" s="2" t="inlineStr">
+      <c r="G243" s="2" t="inlineStr"/>
+      <c r="H243" s="2" t="inlineStr">
         <is>
           <t>96
  Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów
@@ -12885,39 +12986,39 @@
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 12:00:55 +0000</t>
         </is>
       </c>
-      <c r="E242" s="2" t="inlineStr">
+      <c r="E244" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F242" s="2" t="inlineStr">
+      <c r="F244" s="2" t="inlineStr">
         <is>
           <t>Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr"/>
-      <c r="H242" s="2" t="inlineStr">
+      <c r="G244" s="2" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr">
         <is>
           <t>96
  Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs
@@ -12936,39 +13037,39 @@
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="2" t="inlineStr">
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B243" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D243" s="2" t="inlineStr">
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 09:53:57 +0000</t>
         </is>
       </c>
-      <c r="E243" s="2" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F243" s="2" t="inlineStr">
+      <c r="F245" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G243" s="2" t="inlineStr"/>
-      <c r="H243" s="2" t="inlineStr">
+      <c r="G245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -12987,39 +13088,39 @@
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D244" s="2" t="inlineStr">
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 09:08:27 +0000</t>
         </is>
       </c>
-      <c r="E244" s="2" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F244" s="2" t="inlineStr">
+      <c r="F246" s="2" t="inlineStr">
         <is>
           <t>Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise</t>
         </is>
       </c>
-      <c r="G244" s="2" t="inlineStr"/>
-      <c r="H244" s="2" t="inlineStr">
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr">
         <is>
           <t>96
  Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise
@@ -13038,39 +13139,39 @@
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D245" s="2" t="inlineStr">
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 05:08:12 +0000</t>
         </is>
       </c>
-      <c r="E245" s="2" t="inlineStr">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F245" s="2" t="inlineStr">
+      <c r="F247" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 6/2026</t>
         </is>
       </c>
-      <c r="G245" s="2" t="inlineStr"/>
-      <c r="H245" s="2" t="inlineStr">
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 6/2026
  96
@@ -13088,39 +13189,39 @@
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 04:22:50 +0000</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="E248" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F246" s="2" t="inlineStr">
+      <c r="F248" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Verkäufer for 6/2026</t>
         </is>
       </c>
-      <c r="G246" s="2" t="inlineStr"/>
-      <c r="H246" s="2" t="inlineStr">
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.de Rechnungskorrektur Verkäufer for 6/2026
  96
@@ -13144,39 +13245,39 @@
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D247" s="2" t="inlineStr">
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 04:18:37 +0000</t>
         </is>
       </c>
-      <c r="E247" s="2" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F247" s="2" t="inlineStr">
+      <c r="F249" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 6/2026</t>
         </is>
       </c>
-      <c r="G247" s="2" t="inlineStr"/>
-      <c r="H247" s="2" t="inlineStr">
+      <c r="G249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 6/2026
  96
@@ -13203,39 +13304,39 @@
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D248" s="2" t="inlineStr">
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 03:58:57 +0000</t>
         </is>
       </c>
-      <c r="E248" s="2" t="inlineStr">
+      <c r="E250" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F248" s="2" t="inlineStr">
+      <c r="F250" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G248" s="2" t="inlineStr"/>
-      <c r="H248" s="2" t="inlineStr">
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -13262,39 +13363,39 @@
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B249" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D249" s="2" t="inlineStr">
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 03:24:51 +0000</t>
         </is>
       </c>
-      <c r="E249" s="2" t="inlineStr">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F249" s="2" t="inlineStr">
+      <c r="F251" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G249" s="2" t="inlineStr"/>
-      <c r="H249" s="2" t="inlineStr">
+      <c r="G251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 6/2026
  96
@@ -13317,39 +13418,39 @@
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B250" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D250" s="2" t="inlineStr">
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 03:10:44 +0000</t>
         </is>
       </c>
-      <c r="E250" s="2" t="inlineStr">
+      <c r="E252" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F250" s="2" t="inlineStr">
+      <c r="F252" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Verkoper for 6/2026</t>
         </is>
       </c>
-      <c r="G250" s="2" t="inlineStr"/>
-      <c r="H250" s="2" t="inlineStr">
+      <c r="G252" s="2" t="inlineStr"/>
+      <c r="H252" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Verkoper for 6/2026
  96
@@ -13373,39 +13474,39 @@
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B251" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D251" s="2" t="inlineStr">
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 03:00:23 +0000</t>
         </is>
       </c>
-      <c r="E251" s="2" t="inlineStr">
+      <c r="E253" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F251" s="2" t="inlineStr">
+      <c r="F253" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 6/2026</t>
         </is>
       </c>
-      <c r="G251" s="2" t="inlineStr"/>
-      <c r="H251" s="2" t="inlineStr">
+      <c r="G253" s="2" t="inlineStr"/>
+      <c r="H253" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 6/2026
  96
@@ -13432,39 +13533,39 @@
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="2" t="inlineStr">
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B252" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D252" s="2" t="inlineStr">
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 02:41:16 +0000</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="E254" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F252" s="2" t="inlineStr">
+      <c r="F254" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr"/>
-      <c r="H252" s="2" t="inlineStr">
+      <c r="G254" s="2" t="inlineStr"/>
+      <c r="H254" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -13491,39 +13592,39 @@
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="2" t="inlineStr">
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B253" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C253" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D253" s="2" t="inlineStr">
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 02:20:20 +0000</t>
         </is>
       </c>
-      <c r="E253" s="2" t="inlineStr">
+      <c r="E255" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F253" s="2" t="inlineStr">
+      <c r="F255" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Creditnota Verkoper for 6/2026</t>
         </is>
       </c>
-      <c r="G253" s="2" t="inlineStr"/>
-      <c r="H253" s="2" t="inlineStr">
+      <c r="G255" s="2" t="inlineStr"/>
+      <c r="H255" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Creditnota Verkoper for 6/2026
  96
@@ -13543,39 +13644,39 @@
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="2" t="inlineStr">
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B254" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C254" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D254" s="2" t="inlineStr">
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 02:05:26 +0000</t>
         </is>
       </c>
-      <c r="E254" s="2" t="inlineStr">
+      <c r="E256" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F254" s="2" t="inlineStr">
+      <c r="F256" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G254" s="2" t="inlineStr"/>
-      <c r="H254" s="2" t="inlineStr">
+      <c r="G256" s="2" t="inlineStr"/>
+      <c r="H256" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 6/2026
  96
@@ -13598,39 +13699,39 @@
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" s="2" t="inlineStr">
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B255" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C255" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D255" s="2" t="inlineStr">
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 02:01:10 +0000</t>
         </is>
       </c>
-      <c r="E255" s="2" t="inlineStr">
+      <c r="E257" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F255" s="2" t="inlineStr">
+      <c r="F257" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G255" s="2" t="inlineStr"/>
-      <c r="H255" s="2" t="inlineStr">
+      <c r="G257" s="2" t="inlineStr"/>
+      <c r="H257" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -13655,39 +13756,39 @@
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" s="2" t="inlineStr">
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B256" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C256" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D256" s="2" t="inlineStr">
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 00:33:27 +0000</t>
         </is>
       </c>
-      <c r="E256" s="2" t="inlineStr">
+      <c r="E258" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F256" s="2" t="inlineStr">
+      <c r="F258" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G256" s="2" t="inlineStr"/>
-      <c r="H256" s="2" t="inlineStr">
+      <c r="G258" s="2" t="inlineStr"/>
+      <c r="H258" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026
  96
@@ -13706,39 +13807,39 @@
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B257" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C257" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D257" s="2" t="inlineStr">
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 00:22:23 +0000</t>
         </is>
       </c>
-      <c r="E257" s="2" t="inlineStr">
+      <c r="E259" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F257" s="2" t="inlineStr">
+      <c r="F259" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G257" s="2" t="inlineStr"/>
-      <c r="H257" s="2" t="inlineStr">
+      <c r="G259" s="2" t="inlineStr"/>
+      <c r="H259" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 6/2026
  96
@@ -13756,39 +13857,39 @@
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" s="2" t="inlineStr">
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B258" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C258" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D258" s="2" t="inlineStr">
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 00:13:46 +0000</t>
         </is>
       </c>
-      <c r="E258" s="2" t="inlineStr">
+      <c r="E260" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F258" s="2" t="inlineStr">
+      <c r="F260" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G258" s="2" t="inlineStr"/>
-      <c r="H258" s="2" t="inlineStr">
+      <c r="G260" s="2" t="inlineStr"/>
+      <c r="H260" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -13813,39 +13914,39 @@
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="2" t="inlineStr">
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B259" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C259" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D259" s="2" t="inlineStr">
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 23:07:09 +0000</t>
         </is>
       </c>
-      <c r="E259" s="2" t="inlineStr">
+      <c r="E261" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F259" s="2" t="inlineStr">
+      <c r="F261" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G259" s="2" t="inlineStr"/>
-      <c r="H259" s="2" t="inlineStr">
+      <c r="G261" s="2" t="inlineStr"/>
+      <c r="H261" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026
  96
@@ -13864,39 +13965,39 @@
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="2" t="inlineStr">
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B260" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C260" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D260" s="2" t="inlineStr">
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 21:44:31 +0000</t>
         </is>
       </c>
-      <c r="E260" s="2" t="inlineStr">
+      <c r="E262" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F260" s="2" t="inlineStr">
+      <c r="F262" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G260" s="2" t="inlineStr"/>
-      <c r="H260" s="2" t="inlineStr">
+      <c r="G262" s="2" t="inlineStr"/>
+      <c r="H262" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -13921,39 +14022,39 @@
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" s="2" t="inlineStr">
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B261" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C261" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D261" s="2" t="inlineStr">
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 21:29:53 +0000</t>
         </is>
       </c>
-      <c r="E261" s="2" t="inlineStr">
+      <c r="E263" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F261" s="2" t="inlineStr">
+      <c r="F263" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 6/2026</t>
         </is>
       </c>
-      <c r="G261" s="2" t="inlineStr"/>
-      <c r="H261" s="2" t="inlineStr">
+      <c r="G263" s="2" t="inlineStr"/>
+      <c r="H263" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 6/2026
  96
@@ -13978,39 +14079,39 @@
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" s="2" t="inlineStr">
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B262" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C262" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D262" s="2" t="inlineStr">
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 21:23:16 +0000</t>
         </is>
       </c>
-      <c r="E262" s="2" t="inlineStr">
+      <c r="E264" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F262" s="2" t="inlineStr">
+      <c r="F264" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G262" s="2" t="inlineStr"/>
-      <c r="H262" s="2" t="inlineStr">
+      <c r="G264" s="2" t="inlineStr"/>
+      <c r="H264" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026
  96
@@ -14029,39 +14130,39 @@
         </is>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" s="2" t="inlineStr">
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B263" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C263" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D263" s="2" t="inlineStr">
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 21:07:51 +0000</t>
         </is>
       </c>
-      <c r="E263" s="2" t="inlineStr">
+      <c r="E265" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F263" s="2" t="inlineStr">
+      <c r="F265" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G263" s="2" t="inlineStr"/>
-      <c r="H263" s="2" t="inlineStr">
+      <c r="G265" s="2" t="inlineStr"/>
+      <c r="H265" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026
  96
@@ -14088,39 +14189,39 @@
         </is>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" s="2" t="inlineStr">
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B264" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C264" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D264" s="2" t="inlineStr">
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:56:46 +0000</t>
         </is>
       </c>
-      <c r="E264" s="2" t="inlineStr">
+      <c r="E266" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F264" s="2" t="inlineStr">
+      <c r="F266" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G264" s="2" t="inlineStr"/>
-      <c r="H264" s="2" t="inlineStr">
+      <c r="G266" s="2" t="inlineStr"/>
+      <c r="H266" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -14147,39 +14248,39 @@
         </is>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" s="2" t="inlineStr">
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B265" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C265" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D265" s="2" t="inlineStr">
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:36:00 +0000</t>
         </is>
       </c>
-      <c r="E265" s="2" t="inlineStr">
+      <c r="E267" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F265" s="2" t="inlineStr">
+      <c r="F267" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G265" s="2" t="inlineStr"/>
-      <c r="H265" s="2" t="inlineStr">
+      <c r="G267" s="2" t="inlineStr"/>
+      <c r="H267" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -14204,39 +14305,39 @@
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" s="2" t="inlineStr">
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B266" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C266" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D266" s="2" t="inlineStr">
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:27:56 +0000</t>
         </is>
       </c>
-      <c r="E266" s="2" t="inlineStr">
+      <c r="E268" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F266" s="2" t="inlineStr">
+      <c r="F268" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 6/2026</t>
         </is>
       </c>
-      <c r="G266" s="2" t="inlineStr"/>
-      <c r="H266" s="2" t="inlineStr">
+      <c r="G268" s="2" t="inlineStr"/>
+      <c r="H268" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 6/2026
  96
@@ -14263,39 +14364,39 @@
         </is>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" s="2" t="inlineStr">
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B267" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C267" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D267" s="2" t="inlineStr">
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:23:50 +0000</t>
         </is>
       </c>
-      <c r="E267" s="2" t="inlineStr">
+      <c r="E269" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F267" s="2" t="inlineStr">
+      <c r="F269" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G267" s="2" t="inlineStr"/>
-      <c r="H267" s="2" t="inlineStr">
+      <c r="G269" s="2" t="inlineStr"/>
+      <c r="H269" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026
  96
@@ -14319,39 +14420,39 @@
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" s="2" t="inlineStr">
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B268" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C268" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D268" s="2" t="inlineStr">
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:07:18 +0000</t>
         </is>
       </c>
-      <c r="E268" s="2" t="inlineStr">
+      <c r="E270" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F268" s="2" t="inlineStr">
+      <c r="F270" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Säljare for 6/2026</t>
         </is>
       </c>
-      <c r="G268" s="2" t="inlineStr"/>
-      <c r="H268" s="2" t="inlineStr">
+      <c r="G270" s="2" t="inlineStr"/>
+      <c r="H270" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Säljare for 6/2026
  96
@@ -14378,39 +14479,39 @@
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" s="2" t="inlineStr">
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B269" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C269" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D269" s="2" t="inlineStr">
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:02:23 +0000</t>
         </is>
       </c>
-      <c r="E269" s="2" t="inlineStr">
+      <c r="E271" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F269" s="2" t="inlineStr">
+      <c r="F271" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G269" s="2" t="inlineStr"/>
-      <c r="H269" s="2" t="inlineStr">
+      <c r="G271" s="2" t="inlineStr"/>
+      <c r="H271" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026
  96
@@ -14437,39 +14538,39 @@
         </is>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" s="2" t="inlineStr">
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B270" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C270" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D270" s="2" t="inlineStr">
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 19:58:54 +0000</t>
         </is>
       </c>
-      <c r="E270" s="2" t="inlineStr">
+      <c r="E272" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F270" s="2" t="inlineStr">
+      <c r="F272" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G270" s="2" t="inlineStr"/>
-      <c r="H270" s="2" t="inlineStr">
+      <c r="G272" s="2" t="inlineStr"/>
+      <c r="H272" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -14496,39 +14597,39 @@
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" s="2" t="inlineStr">
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B271" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C271" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D271" s="2" t="inlineStr">
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 19:55:57 +0000</t>
         </is>
       </c>
-      <c r="E271" s="2" t="inlineStr">
+      <c r="E273" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F271" s="2" t="inlineStr">
+      <c r="F273" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Verkoper for 6/2026</t>
         </is>
       </c>
-      <c r="G271" s="2" t="inlineStr"/>
-      <c r="H271" s="2" t="inlineStr">
+      <c r="G273" s="2" t="inlineStr"/>
+      <c r="H273" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Verkoper for 6/2026
  96
@@ -14553,39 +14654,39 @@
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" s="2" t="inlineStr">
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B272" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C272" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D272" s="2" t="inlineStr">
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 19:16:22 +0000</t>
         </is>
       </c>
-      <c r="E272" s="2" t="inlineStr">
+      <c r="E274" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F272" s="2" t="inlineStr">
+      <c r="F274" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G272" s="2" t="inlineStr"/>
-      <c r="H272" s="2" t="inlineStr">
+      <c r="G274" s="2" t="inlineStr"/>
+      <c r="H274" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -14612,39 +14713,39 @@
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="2" t="inlineStr">
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B273" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C273" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D273" s="2" t="inlineStr">
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 19:05:55 +0000</t>
         </is>
       </c>
-      <c r="E273" s="2" t="inlineStr">
+      <c r="E275" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F273" s="2" t="inlineStr">
+      <c r="F275" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Sprzedawcy for 6/2026</t>
         </is>
       </c>
-      <c r="G273" s="2" t="inlineStr"/>
-      <c r="H273" s="2" t="inlineStr">
+      <c r="G275" s="2" t="inlineStr"/>
+      <c r="H275" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Sprzedawcy for 6/2026
  96
@@ -14669,39 +14770,39 @@
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" s="2" t="inlineStr">
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B274" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C274" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D274" s="2" t="inlineStr">
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 18:55:02 +0000</t>
         </is>
       </c>
-      <c r="E274" s="2" t="inlineStr">
+      <c r="E276" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F274" s="2" t="inlineStr">
+      <c r="F276" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G274" s="2" t="inlineStr"/>
-      <c r="H274" s="2" t="inlineStr">
+      <c r="G276" s="2" t="inlineStr"/>
+      <c r="H276" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 6/2026
  96
@@ -14719,39 +14820,39 @@
         </is>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" s="2" t="inlineStr">
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B275" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C275" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D275" s="2" t="inlineStr">
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 18:14:51 +0000</t>
         </is>
       </c>
-      <c r="E275" s="2" t="inlineStr">
+      <c r="E277" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F275" s="2" t="inlineStr">
+      <c r="F277" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G275" s="2" t="inlineStr"/>
-      <c r="H275" s="2" t="inlineStr">
+      <c r="G277" s="2" t="inlineStr"/>
+      <c r="H277" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026
  96
@@ -14775,39 +14876,39 @@
         </is>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" s="2" t="inlineStr">
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B276" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C276" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D276" s="2" t="inlineStr">
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:47:27 +0000</t>
         </is>
       </c>
-      <c r="E276" s="2" t="inlineStr">
+      <c r="E278" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F276" s="2" t="inlineStr">
+      <c r="F278" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G276" s="2" t="inlineStr"/>
-      <c r="H276" s="2" t="inlineStr">
+      <c r="G278" s="2" t="inlineStr"/>
+      <c r="H278" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026
  96
@@ -14834,39 +14935,39 @@
         </is>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" s="2" t="inlineStr">
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B277" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C277" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D277" s="2" t="inlineStr">
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:46:42 +0000</t>
         </is>
       </c>
-      <c r="E277" s="2" t="inlineStr">
+      <c r="E279" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F277" s="2" t="inlineStr">
+      <c r="F279" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G277" s="2" t="inlineStr"/>
-      <c r="H277" s="2" t="inlineStr">
+      <c r="G279" s="2" t="inlineStr"/>
+      <c r="H279" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 6/2026
  96
@@ -14884,39 +14985,39 @@
         </is>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" s="2" t="inlineStr">
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B278" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C278" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D278" s="2" t="inlineStr">
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:31:36 +0000</t>
         </is>
       </c>
-      <c r="E278" s="2" t="inlineStr">
+      <c r="E280" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F278" s="2" t="inlineStr">
+      <c r="F280" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G278" s="2" t="inlineStr"/>
-      <c r="H278" s="2" t="inlineStr">
+      <c r="G280" s="2" t="inlineStr"/>
+      <c r="H280" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -14941,39 +15042,39 @@
         </is>
       </c>
     </row>
-    <row r="279">
-      <c r="A279" s="2" t="inlineStr">
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B279" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C279" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D279" s="2" t="inlineStr">
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:28:53 +0000</t>
         </is>
       </c>
-      <c r="E279" s="2" t="inlineStr">
+      <c r="E281" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F279" s="2" t="inlineStr">
+      <c r="F281" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G279" s="2" t="inlineStr"/>
-      <c r="H279" s="2" t="inlineStr">
+      <c r="G281" s="2" t="inlineStr"/>
+      <c r="H281" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 6/2026
  96
@@ -14991,39 +15092,39 @@
         </is>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" s="2" t="inlineStr">
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B280" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C280" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D280" s="2" t="inlineStr">
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:10:41 +0000</t>
         </is>
       </c>
-      <c r="E280" s="2" t="inlineStr">
+      <c r="E282" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F280" s="2" t="inlineStr">
+      <c r="F282" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G280" s="2" t="inlineStr"/>
-      <c r="H280" s="2" t="inlineStr">
+      <c r="G282" s="2" t="inlineStr"/>
+      <c r="H282" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026
  96
@@ -15047,39 +15148,39 @@
         </is>
       </c>
     </row>
-    <row r="281">
-      <c r="A281" s="2" t="inlineStr">
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B281" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C281" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D281" s="2" t="inlineStr">
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:01:49 +0000</t>
         </is>
       </c>
-      <c r="E281" s="2" t="inlineStr">
+      <c r="E283" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F281" s="2" t="inlineStr">
+      <c r="F283" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G281" s="2" t="inlineStr"/>
-      <c r="H281" s="2" t="inlineStr">
+      <c r="G283" s="2" t="inlineStr"/>
+      <c r="H283" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 6/2026
  96
@@ -15097,39 +15198,39 @@
         </is>
       </c>
     </row>
-    <row r="282">
-      <c r="A282" s="2" t="inlineStr">
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B282" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C282" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D282" s="2" t="inlineStr">
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 16:42:42 +0000</t>
         </is>
       </c>
-      <c r="E282" s="2" t="inlineStr">
+      <c r="E284" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F282" s="2" t="inlineStr">
+      <c r="F284" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G282" s="2" t="inlineStr"/>
-      <c r="H282" s="2" t="inlineStr">
+      <c r="G284" s="2" t="inlineStr"/>
+      <c r="H284" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 6/2026
  96
@@ -15147,39 +15248,39 @@
         </is>
       </c>
     </row>
-    <row r="283">
-      <c r="A283" s="2" t="inlineStr">
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B283" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C283" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D283" s="2" t="inlineStr">
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 16:21:50 +0000</t>
         </is>
       </c>
-      <c r="E283" s="2" t="inlineStr">
+      <c r="E285" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F283" s="2" t="inlineStr">
+      <c r="F285" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G283" s="2" t="inlineStr"/>
-      <c r="H283" s="2" t="inlineStr">
+      <c r="G285" s="2" t="inlineStr"/>
+      <c r="H285" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -15206,39 +15307,39 @@
         </is>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" s="2" t="inlineStr">
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B284" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C284" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D284" s="2" t="inlineStr">
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 16:02:53 +0000</t>
         </is>
       </c>
-      <c r="E284" s="2" t="inlineStr">
+      <c r="E286" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F284" s="2" t="inlineStr">
+      <c r="F286" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G284" s="2" t="inlineStr"/>
-      <c r="H284" s="2" t="inlineStr">
+      <c r="G286" s="2" t="inlineStr"/>
+      <c r="H286" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -15263,40 +15364,40 @@
         </is>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" s="2" t="inlineStr">
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B285" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C285" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D285" s="2" t="inlineStr">
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 15:46:03 +0000</t>
         </is>
       </c>
-      <c r="E285" s="2" t="inlineStr">
+      <c r="E287" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F285" s="2" t="inlineStr">
+      <c r="F287" s="2" t="inlineStr">
         <is>
           <t>Your VAT invoice for EPR Pay on Behalf charges for Amazon.co.uk
  sales</t>
         </is>
       </c>
-      <c r="G285" s="2" t="inlineStr"/>
-      <c r="H285" s="2" t="inlineStr">
+      <c r="G287" s="2" t="inlineStr"/>
+      <c r="H287" s="2" t="inlineStr">
         <is>
           <t>Your VAT invoice for EPR Pay on Behalf charges for Amazon.co.uk sales
  96
@@ -15311,39 +15412,39 @@
         </is>
       </c>
     </row>
-    <row r="286">
-      <c r="A286" s="2" t="inlineStr">
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B286" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C286" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D286" s="2" t="inlineStr">
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 15:40:18 +0000</t>
         </is>
       </c>
-      <c r="E286" s="2" t="inlineStr">
+      <c r="E288" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F286" s="2" t="inlineStr">
+      <c r="F288" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Verkoper for 6/2026</t>
         </is>
       </c>
-      <c r="G286" s="2" t="inlineStr"/>
-      <c r="H286" s="2" t="inlineStr">
+      <c r="G288" s="2" t="inlineStr"/>
+      <c r="H288" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Verkoper for 6/2026
  96
@@ -15364,39 +15465,39 @@
         </is>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" s="2" t="inlineStr">
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B287" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C287" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D287" s="2" t="inlineStr">
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 15:35:08 +0000</t>
         </is>
       </c>
-      <c r="E287" s="2" t="inlineStr">
+      <c r="E289" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F287" s="2" t="inlineStr">
+      <c r="F289" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G287" s="2" t="inlineStr"/>
-      <c r="H287" s="2" t="inlineStr">
+      <c r="G289" s="2" t="inlineStr"/>
+      <c r="H289" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026
  96
@@ -15420,39 +15521,39 @@
         </is>
       </c>
     </row>
-    <row r="288">
-      <c r="A288" s="2" t="inlineStr">
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B288" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C288" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D288" s="2" t="inlineStr">
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 15:30:53 +0000</t>
         </is>
       </c>
-      <c r="E288" s="2" t="inlineStr">
+      <c r="E290" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F288" s="2" t="inlineStr">
+      <c r="F290" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G288" s="2" t="inlineStr"/>
-      <c r="H288" s="2" t="inlineStr">
+      <c r="G290" s="2" t="inlineStr"/>
+      <c r="H290" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 6/2026
  96
@@ -15470,39 +15571,39 @@
         </is>
       </c>
     </row>
-    <row r="289">
-      <c r="A289" s="2" t="inlineStr">
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B289" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C289" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D289" s="2" t="inlineStr">
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 14:51:08 +0000</t>
         </is>
       </c>
-      <c r="E289" s="2" t="inlineStr">
+      <c r="E291" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F289" s="2" t="inlineStr">
+      <c r="F291" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G289" s="2" t="inlineStr"/>
-      <c r="H289" s="2" t="inlineStr">
+      <c r="G291" s="2" t="inlineStr"/>
+      <c r="H291" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 6/2026
  96
@@ -15525,39 +15626,39 @@
         </is>
       </c>
     </row>
-    <row r="290">
-      <c r="A290" s="2" t="inlineStr">
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B290" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C290" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D290" s="2" t="inlineStr">
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Jul 2026 04:55:01 +0000</t>
         </is>
       </c>
-      <c r="E290" s="2" t="inlineStr">
+      <c r="E292" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F290" s="2" t="inlineStr">
+      <c r="F292" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G290" s="2" t="inlineStr"/>
-      <c r="H290" s="2" t="inlineStr">
+      <c r="G292" s="2" t="inlineStr"/>
+      <c r="H292" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -15580,39 +15681,39 @@
         </is>
       </c>
     </row>
-    <row r="291">
-      <c r="A291" s="2" t="inlineStr">
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B291" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C291" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D291" s="2" t="inlineStr">
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Jul 2026 04:23:46 +0000</t>
         </is>
       </c>
-      <c r="E291" s="2" t="inlineStr">
+      <c r="E293" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F291" s="2" t="inlineStr">
+      <c r="F293" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G291" s="2" t="inlineStr"/>
-      <c r="H291" s="2" t="inlineStr">
+      <c r="G293" s="2" t="inlineStr"/>
+      <c r="H293" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -15636,39 +15737,39 @@
         </is>
       </c>
     </row>
-    <row r="292">
-      <c r="A292" s="2" t="inlineStr">
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B292" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C292" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D292" s="2" t="inlineStr">
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Jul 2026 04:07:00 +0000</t>
         </is>
       </c>
-      <c r="E292" s="2" t="inlineStr">
+      <c r="E294" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F292" s="2" t="inlineStr">
+      <c r="F294" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-08-06</t>
         </is>
       </c>
-      <c r="G292" s="2" t="inlineStr"/>
-      <c r="H292" s="2" t="inlineStr">
+      <c r="G294" s="2" t="inlineStr"/>
+      <c r="H294" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -15690,39 +15791,39 @@
         </is>
       </c>
     </row>
-    <row r="293">
-      <c r="A293" s="2" t="inlineStr">
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B293" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C293" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D293" s="2" t="inlineStr">
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Jul 2026 03:44:53 +0000</t>
         </is>
       </c>
-      <c r="E293" s="2" t="inlineStr">
+      <c r="E295" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F293" s="2" t="inlineStr">
+      <c r="F295" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-08-06</t>
         </is>
       </c>
-      <c r="G293" s="2" t="inlineStr"/>
-      <c r="H293" s="2" t="inlineStr">
+      <c r="G295" s="2" t="inlineStr"/>
+      <c r="H295" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -15746,39 +15847,39 @@
         </is>
       </c>
     </row>
-    <row r="294">
-      <c r="A294" s="2" t="inlineStr">
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B294" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C294" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D294" s="2" t="inlineStr">
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Jul 2026 04:29:33 +0000</t>
         </is>
       </c>
-      <c r="E294" s="2" t="inlineStr">
+      <c r="E296" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F294" s="2" t="inlineStr">
+      <c r="F296" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-30</t>
         </is>
       </c>
-      <c r="G294" s="2" t="inlineStr"/>
-      <c r="H294" s="2" t="inlineStr">
+      <c r="G296" s="2" t="inlineStr"/>
+      <c r="H296" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -15801,39 +15902,39 @@
         </is>
       </c>
     </row>
-    <row r="295">
-      <c r="A295" s="2" t="inlineStr">
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B295" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C295" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D295" s="2" t="inlineStr">
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Jul 2026 04:12:27 +0000</t>
         </is>
       </c>
-      <c r="E295" s="2" t="inlineStr">
+      <c r="E297" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F295" s="2" t="inlineStr">
+      <c r="F297" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G295" s="2" t="inlineStr"/>
-      <c r="H295" s="2" t="inlineStr">
+      <c r="G297" s="2" t="inlineStr"/>
+      <c r="H297" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -15858,39 +15959,39 @@
         </is>
       </c>
     </row>
-    <row r="296">
-      <c r="A296" s="2" t="inlineStr">
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B296" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C296" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D296" s="2" t="inlineStr">
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Jul 2026 03:41:39 +0000</t>
         </is>
       </c>
-      <c r="E296" s="2" t="inlineStr">
+      <c r="E298" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F296" s="2" t="inlineStr">
+      <c r="F298" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G296" s="2" t="inlineStr"/>
-      <c r="H296" s="2" t="inlineStr">
+      <c r="G298" s="2" t="inlineStr"/>
+      <c r="H298" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -15913,39 +16014,39 @@
         </is>
       </c>
     </row>
-    <row r="297">
-      <c r="A297" s="2" t="inlineStr">
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B297" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C297" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D297" s="2" t="inlineStr">
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 04:26:29 +0000</t>
         </is>
       </c>
-      <c r="E297" s="2" t="inlineStr">
+      <c r="E299" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F297" s="2" t="inlineStr">
+      <c r="F299" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-23</t>
         </is>
       </c>
-      <c r="G297" s="2" t="inlineStr"/>
-      <c r="H297" s="2" t="inlineStr">
+      <c r="G299" s="2" t="inlineStr"/>
+      <c r="H299" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -15966,39 +16067,39 @@
         </is>
       </c>
     </row>
-    <row r="298">
-      <c r="A298" s="2" t="inlineStr">
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B298" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C298" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D298" s="2" t="inlineStr">
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 04:08:56 +0000</t>
         </is>
       </c>
-      <c r="E298" s="2" t="inlineStr">
+      <c r="E300" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F298" s="2" t="inlineStr">
+      <c r="F300" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G298" s="2" t="inlineStr"/>
-      <c r="H298" s="2" t="inlineStr">
+      <c r="G300" s="2" t="inlineStr"/>
+      <c r="H300" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -16021,39 +16122,39 @@
         </is>
       </c>
     </row>
-    <row r="299">
-      <c r="A299" s="2" t="inlineStr">
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B299" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C299" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D299" s="2" t="inlineStr">
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 03:06:39 +0000</t>
         </is>
       </c>
-      <c r="E299" s="2" t="inlineStr">
+      <c r="E301" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F299" s="2" t="inlineStr">
+      <c r="F301" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-23</t>
         </is>
       </c>
-      <c r="G299" s="2" t="inlineStr"/>
-      <c r="H299" s="2" t="inlineStr">
+      <c r="G301" s="2" t="inlineStr"/>
+      <c r="H301" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -16076,39 +16177,39 @@
         </is>
       </c>
     </row>
-    <row r="300">
-      <c r="A300" s="2" t="inlineStr">
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B300" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C300" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D300" s="2" t="inlineStr">
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Jul 2026 14:32:02 +0000</t>
         </is>
       </c>
-      <c r="E300" s="2" t="inlineStr">
+      <c r="E302" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F300" s="2" t="inlineStr">
+      <c r="F302" s="2" t="inlineStr">
         <is>
           <t>Add WhatsApp to your notification preferences</t>
         </is>
       </c>
-      <c r="G300" s="2" t="inlineStr"/>
-      <c r="H300" s="2" t="inlineStr">
+      <c r="G302" s="2" t="inlineStr"/>
+      <c r="H302" s="2" t="inlineStr">
         <is>
           <t>96
  Stay connected with account updates on WhatsApp—opt in today to get started
@@ -16125,39 +16226,39 @@
         </is>
       </c>
     </row>
-    <row r="301">
-      <c r="A301" s="2" t="inlineStr">
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B301" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C301" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D301" s="2" t="inlineStr">
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 17:52:32 +0000</t>
         </is>
       </c>
-      <c r="E301" s="2" t="inlineStr">
+      <c r="E303" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F301" s="2" t="inlineStr">
+      <c r="F303" s="2" t="inlineStr">
         <is>
           <t>Get faster, personalized support with Seller Assistant</t>
         </is>
       </c>
-      <c r="G301" s="2" t="inlineStr"/>
-      <c r="H301" s="2" t="inlineStr">
+      <c r="G303" s="2" t="inlineStr"/>
+      <c r="H303" s="2" t="inlineStr">
         <is>
           <t>96
  When you click Get help and resources, you’ll be directed to Seller Assistant, our AI-powered assistant.
@@ -16169,39 +16270,39 @@
         </is>
       </c>
     </row>
-    <row r="302">
-      <c r="A302" s="2" t="inlineStr">
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B302" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C302" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D302" s="2" t="inlineStr">
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 05:44:42 +0000</t>
         </is>
       </c>
-      <c r="E302" s="2" t="inlineStr">
+      <c r="E304" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F302" s="2" t="inlineStr">
+      <c r="F304" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">【重要】西班牙VAT通知期延期指南。税号激活用时最长达37周，请立即行动以免影响销售 </t>
         </is>
       </c>
-      <c r="G302" s="2" t="inlineStr"/>
-      <c r="H302" s="2" t="inlineStr">
+      <c r="G304" s="2" t="inlineStr"/>
+      <c r="H304" s="2" t="inlineStr">
         <is>
           <t>西班牙延期政策更新：已过通知期也可发起申请
 			尊敬的 深圳市微海众信科技有限公司,
@@ -16237,39 +16338,39 @@
         </is>
       </c>
     </row>
-    <row r="303">
-      <c r="A303" s="2" t="inlineStr">
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B303" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C303" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D303" s="2" t="inlineStr">
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Jul 2026 15:32:18 +0000</t>
         </is>
       </c>
-      <c r="E303" s="2" t="inlineStr">
+      <c r="E305" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F303" s="2" t="inlineStr">
+      <c r="F305" s="2" t="inlineStr">
         <is>
           <t>Accelerate 2026: Sessions designed for where you are and where you’re going</t>
         </is>
       </c>
-      <c r="G303" s="2" t="inlineStr"/>
-      <c r="H303" s="2" t="inlineStr">
+      <c r="G305" s="2" t="inlineStr"/>
+      <c r="H305" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-14/7z4n1pf/6770773185/h/WdBYUGZo6UnxZlR8bvark7SKCv06gleKjoxG039m7cg)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4n1pj/6770773185/h/WdBYUGZo6UnxZlR8bvark7SKCv06gleKjoxG039m7cg)
@@ -16281,39 +16382,39 @@
         </is>
       </c>
     </row>
-    <row r="304">
-      <c r="A304" s="2" t="inlineStr">
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B304" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C304" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D304" s="2" t="inlineStr">
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Jul 2026 15:11:01 +0000</t>
         </is>
       </c>
-      <c r="E304" s="2" t="inlineStr">
+      <c r="E306" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F304" s="2" t="inlineStr">
+      <c r="F306" s="2" t="inlineStr">
         <is>
           <t>Your Accelerate 2026 session catalog is now live</t>
         </is>
       </c>
-      <c r="G304" s="2" t="inlineStr"/>
-      <c r="H304" s="2" t="inlineStr">
+      <c r="G306" s="2" t="inlineStr"/>
+      <c r="H306" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-14/7z4n1s7/6767228964/h/eXAL3anI3dWEgFXK_p_u6QFSTde6SYcFg0MO4Yodnjk)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4n1sb/6767228964/h/eXAL3anI3dWEgFXK_p_u6QFSTde6SYcFg0MO4Yodnjk)
@@ -16325,40 +16426,40 @@
         </is>
       </c>
     </row>
-    <row r="305">
-      <c r="A305" s="2" t="inlineStr">
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B305" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C305" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D305" s="2" t="inlineStr">
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 03:21:27 +0000</t>
         </is>
       </c>
-      <c r="E305" s="2" t="inlineStr">
+      <c r="E307" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Communications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F305" s="2" t="inlineStr">
+      <c r="F307" s="2" t="inlineStr">
         <is>
           <t>[Amazon.co.uk] One or More of Your Amazon Listings Have Been Search
  Suppressed</t>
         </is>
       </c>
-      <c r="G305" s="2" t="inlineStr"/>
-      <c r="H305" s="2" t="inlineStr">
+      <c r="G307" s="2" t="inlineStr"/>
+      <c r="H307" s="2" t="inlineStr">
         <is>
           <t>96
 [Amazon.co.uk] One or More of Your Amazon Listings Have Been Search Suppressed
